--- a/customers/sobhan.xlsx
+++ b/customers/sobhan.xlsx
@@ -669,7 +669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.625" customWidth="1"/>
@@ -680,7 +680,7 @@
     <col min="6" max="6" width="18.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -689,7 +689,7 @@
       </c>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
@@ -705,8 +705,12 @@
       <c r="E2" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H2" s="11">
+        <f>C55</f>
+        <v>1437000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="10">
         <f xml:space="preserve"> B3</f>
         <v>994000</v>
@@ -720,7 +724,7 @@
       </c>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <f xml:space="preserve"> A3 + B4-C4</f>
         <v>527000</v>
@@ -734,7 +738,7 @@
       </c>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <f t="shared" ref="A5:A15" si="0" xml:space="preserve"> A4 + B5-C5</f>
         <v>564000</v>
@@ -750,7 +754,7 @@
         <v>38012</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <f t="shared" si="0"/>
         <v>684000</v>
@@ -766,7 +770,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <f t="shared" si="0"/>
         <v>534000</v>
@@ -782,7 +786,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <f t="shared" si="0"/>
         <v>631000</v>
@@ -798,7 +802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <f t="shared" si="0"/>
         <v>700000</v>
@@ -814,7 +818,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <f t="shared" si="0"/>
         <v>828500</v>
@@ -830,7 +834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <f t="shared" si="0"/>
         <v>883500</v>
@@ -846,7 +850,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <f t="shared" si="0"/>
         <v>908500</v>
@@ -862,7 +866,7 @@
         <v>38023</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <f t="shared" si="0"/>
         <v>933500</v>
@@ -878,7 +882,7 @@
         <v>38024</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <f t="shared" si="0"/>
         <v>1048500</v>
@@ -894,7 +898,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <f t="shared" si="0"/>
         <v>1148500</v>
@@ -910,7 +914,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="11"/>
       <c r="B16" s="11">
         <f xml:space="preserve"> B3 + B4 + B5 + B6 + B7 + B8 + B9 +B10 + B11 + B12 + B13 + B14 + B15</f>
@@ -1277,7 +1281,7 @@
     </row>
     <row r="43" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="10">
-        <f t="shared" ref="A43:A53" si="2" xml:space="preserve"> A42 + B43-C43</f>
+        <f t="shared" ref="A43:A52" si="2" xml:space="preserve"> A42 + B43-C43</f>
         <v>1942000</v>
       </c>
       <c r="B43" s="10">
